--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,59 +680,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136637408</v>
+        <v>136662367</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>80452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mjöberget norrsluttning, Hls</t>
+          <t>Mjöberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542450</v>
+        <v>542452</v>
       </c>
       <c r="R2" t="n">
-        <v>6839795</v>
+        <v>6839801</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -774,72 +774,94 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637408</t>
+          <t>https://artportalen.se/Sighting/136662367</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136637533</v>
+        <v>136662434</v>
       </c>
       <c r="B3" t="n">
-        <v>96557</v>
+        <v>80452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mjöberget norrsluttning, Hls</t>
+          <t>Mjöberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542476</v>
+        <v>542443</v>
       </c>
       <c r="R3" t="n">
-        <v>6839720</v>
+        <v>6839775</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,30 +903,45 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637533</t>
+          <t>https://artportalen.se/Sighting/136662434</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136637626</v>
+        <v>136665586</v>
       </c>
       <c r="B4" t="n">
-        <v>99342</v>
+        <v>80452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,53 +949,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mjöberget norrsluttning, Hls</t>
+          <t>Mjöberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542512</v>
+        <v>542404</v>
       </c>
       <c r="R4" t="n">
-        <v>6839760</v>
+        <v>6839722</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,11 +1020,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sex överblommade stjälkar. En knärotskoloni som tydligt tagit skada av uttorkning och exponering efter att en väg byggts bara ca 30 m från den.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,19 +1032,1101 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136665586</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136665690</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80452</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>392</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>542338</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6839706</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136665690</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136637408</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92113</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mjöberget norrsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>542450</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6839795</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carina Frost, Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136637408</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136637533</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96557</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mjöberget norrsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>542476</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6839720</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136637533</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136662522</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96557</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>542444</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6839767</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136662522</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136665695</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96557</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>542338</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6839706</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136665695</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136662397</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80483</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>542452</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6839779</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136662397</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136665455</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80483</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>542418</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6839748</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136665455</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136665683</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80483</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>542338</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6839706</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136665683</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136637626</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mjöberget norrsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>542512</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6839760</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Sex överblommade stjälkar. En knärotskoloni som tydligt tagit skada av uttorkning och exponering efter att en väg byggts bara ca 30 m från den.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Carina Frost, Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136637626</t>
         </is>
@@ -1028,6 +2137,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,59 +1188,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136637408</v>
+        <v>136694564</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>80452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>392</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mjöberget norrsluttning, Hls</t>
+          <t>Mjöberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542450</v>
+        <v>542327</v>
       </c>
       <c r="R6" t="n">
-        <v>6839795</v>
+        <v>6839655</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1270,6 +1262,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ymnigt på asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,27 +1282,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637408</t>
+          <t>https://artportalen.se/Sighting/136694564</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136637533</v>
+        <v>136637408</v>
       </c>
       <c r="B7" t="n">
-        <v>96557</v>
+        <v>92116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,27 +1310,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1341,10 +1345,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542476</v>
+        <v>542450</v>
       </c>
       <c r="R7" t="n">
-        <v>6839720</v>
+        <v>6839795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,22 +1401,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637533</t>
+          <t>https://artportalen.se/Sighting/136637408</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136662522</v>
+        <v>136637533</v>
       </c>
       <c r="B8" t="n">
-        <v>96557</v>
+        <v>96560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,32 +1441,24 @@
           <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mjöberget, Hls</t>
+          <t>Mjöberget norrsluttning, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542444</v>
+        <v>542476</v>
       </c>
       <c r="R8" t="n">
-        <v>6839767</v>
+        <v>6839720</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1507,27 +1503,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136662522</t>
+          <t>https://artportalen.se/Sighting/136637533</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136665695</v>
+        <v>136662522</v>
       </c>
       <c r="B9" t="n">
-        <v>96557</v>
+        <v>96560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,8 +1548,16 @@
           <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1563,10 +1567,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542338</v>
+        <v>542444</v>
       </c>
       <c r="R9" t="n">
-        <v>6839706</v>
+        <v>6839767</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1625,16 +1629,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665695</t>
+          <t>https://artportalen.se/Sighting/136662522</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136662397</v>
+        <v>136665695</v>
       </c>
       <c r="B10" t="n">
-        <v>80483</v>
+        <v>96560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,26 +1646,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542452</v>
+        <v>542338</v>
       </c>
       <c r="R10" t="n">
-        <v>6839779</v>
+        <v>6839706</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1717,21 +1722,6 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1746,13 +1736,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136662397</t>
+          <t>https://artportalen.se/Sighting/136665695</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136665455</v>
+        <v>136662397</v>
       </c>
       <c r="B11" t="n">
         <v>80483</v>
@@ -1780,16 +1770,8 @@
           <t>(Dicks.) Nyl.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1798,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542418</v>
+        <v>542452</v>
       </c>
       <c r="R11" t="n">
-        <v>6839748</v>
+        <v>6839779</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1875,13 +1857,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665455</t>
+          <t>https://artportalen.se/Sighting/136662397</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136665683</v>
+        <v>136665455</v>
       </c>
       <c r="B12" t="n">
         <v>80483</v>
@@ -1911,7 +1893,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1927,10 +1909,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542338</v>
+        <v>542418</v>
       </c>
       <c r="R12" t="n">
-        <v>6839706</v>
+        <v>6839748</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2004,70 +1986,65 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665683</t>
+          <t>https://artportalen.se/Sighting/136665455</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136637626</v>
+        <v>136665683</v>
       </c>
       <c r="B13" t="n">
-        <v>99342</v>
+        <v>80483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mjöberget norrsluttning, Hls</t>
+          <t>Mjöberget, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542512</v>
+        <v>542338</v>
       </c>
       <c r="R13" t="n">
-        <v>6839760</v>
+        <v>6839706</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2097,11 +2074,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Sex överblommade stjälkar. En knärotskoloni som tydligt tagit skada av uttorkning och exponering efter att en väg byggts bara ca 30 m från den.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2114,21 +2086,509 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136665683</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136694561</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80483</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>542327</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6839655</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ymnigt på asp</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136694561</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136637626</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99345</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mjöberget norrsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>542512</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6839760</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sex överblommade stjälkar. En knärotskoloni som tydligt tagit skada av uttorkning och exponering efter att en väg byggts bara ca 30 m från den.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Carina Frost, Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136637626</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136694832</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80539</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>542394</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6839595</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Grov asp</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136694832</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136694923</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80539</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>542509</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6839587</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Grov asp</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136694923</t>
         </is>
       </c>
     </row>
@@ -2146,6 +2606,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -1302,7 +1302,7 @@
         <v>136637408</v>
       </c>
       <c r="B7" t="n">
-        <v>92116</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136637533</v>
       </c>
       <c r="B8" t="n">
-        <v>96560</v>
+        <v>96561</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>136662522</v>
       </c>
       <c r="B9" t="n">
-        <v>96560</v>
+        <v>96561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136665695</v>
       </c>
       <c r="B10" t="n">
-        <v>96560</v>
+        <v>96561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>136637626</v>
       </c>
       <c r="B15" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662367</v>
       </c>
       <c r="B2" t="n">
-        <v>80452</v>
+        <v>80454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>136662434</v>
       </c>
       <c r="B3" t="n">
-        <v>80452</v>
+        <v>80454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>136665586</v>
       </c>
       <c r="B4" t="n">
-        <v>80452</v>
+        <v>80454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>136665690</v>
       </c>
       <c r="B5" t="n">
-        <v>80452</v>
+        <v>80454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136694564</v>
       </c>
       <c r="B6" t="n">
-        <v>80452</v>
+        <v>80454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>136637408</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136637533</v>
       </c>
       <c r="B8" t="n">
-        <v>96561</v>
+        <v>96566</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>136662522</v>
       </c>
       <c r="B9" t="n">
-        <v>96561</v>
+        <v>96566</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136665695</v>
       </c>
       <c r="B10" t="n">
-        <v>96561</v>
+        <v>96566</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>136662397</v>
       </c>
       <c r="B11" t="n">
-        <v>80483</v>
+        <v>80485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136665455</v>
       </c>
       <c r="B12" t="n">
-        <v>80483</v>
+        <v>80485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>136665683</v>
       </c>
       <c r="B13" t="n">
-        <v>80483</v>
+        <v>80485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>136694561</v>
       </c>
       <c r="B14" t="n">
-        <v>80483</v>
+        <v>80485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>136637626</v>
       </c>
       <c r="B15" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>136694832</v>
       </c>
       <c r="B16" t="n">
-        <v>80539</v>
+        <v>80541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>136694923</v>
       </c>
       <c r="B17" t="n">
-        <v>80539</v>
+        <v>80541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -1302,7 +1302,7 @@
         <v>136637408</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136637533</v>
       </c>
       <c r="B8" t="n">
-        <v>96566</v>
+        <v>96568</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>136662522</v>
       </c>
       <c r="B9" t="n">
-        <v>96566</v>
+        <v>96568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136665695</v>
       </c>
       <c r="B10" t="n">
-        <v>96566</v>
+        <v>96568</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>136637626</v>
       </c>
       <c r="B15" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1299,59 +1299,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136637408</v>
+        <v>136920950</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>80454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>392</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mjöberget norrsluttning, Hls</t>
+          <t>Mjöberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542450</v>
+        <v>542474</v>
       </c>
       <c r="R7" t="n">
-        <v>6839795</v>
+        <v>6839441</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1396,69 +1396,76 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637408</t>
+          <t>https://artportalen.se/Sighting/136920950</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136637533</v>
+        <v>136920976</v>
       </c>
       <c r="B8" t="n">
-        <v>96568</v>
+        <v>80454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>392</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mjöberget norrsluttning, Hls</t>
+          <t>Mjöberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542476</v>
+        <v>542517</v>
       </c>
       <c r="R8" t="n">
-        <v>6839720</v>
+        <v>6839397</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1503,63 +1510,62 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637533</t>
+          <t>https://artportalen.se/Sighting/136920976</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136662522</v>
+        <v>136921075</v>
       </c>
       <c r="B9" t="n">
-        <v>96568</v>
+        <v>80454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1567,10 +1573,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542444</v>
+        <v>542584</v>
       </c>
       <c r="R9" t="n">
-        <v>6839767</v>
+        <v>6839474</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1629,44 +1635,43 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136662522</t>
+          <t>https://artportalen.se/Sighting/136921075</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136665695</v>
+        <v>136921117</v>
       </c>
       <c r="B10" t="n">
-        <v>96568</v>
+        <v>80454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>392</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542338</v>
+        <v>542588</v>
       </c>
       <c r="R10" t="n">
-        <v>6839706</v>
+        <v>6839473</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1712,6 +1717,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ymnigt</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1736,38 +1746,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665695</t>
+          <t>https://artportalen.se/Sighting/136921117</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136662397</v>
+        <v>136921309</v>
       </c>
       <c r="B11" t="n">
-        <v>80485</v>
+        <v>80454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,10 +1790,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542452</v>
+        <v>542484</v>
       </c>
       <c r="R11" t="n">
-        <v>6839779</v>
+        <v>6839710</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,21 +1838,6 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1857,48 +1852,48 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136662397</t>
+          <t>https://artportalen.se/Sighting/136921309</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136665455</v>
+        <v>136921370</v>
       </c>
       <c r="B12" t="n">
-        <v>80485</v>
+        <v>80454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1909,10 +1904,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542418</v>
+        <v>542587</v>
       </c>
       <c r="R12" t="n">
-        <v>6839748</v>
+        <v>6839433</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1957,21 +1952,6 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
@@ -1980,22 +1960,22 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665455</t>
+          <t>https://artportalen.se/Sighting/136921370</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136665683</v>
+        <v>136637408</v>
       </c>
       <c r="B13" t="n">
-        <v>80485</v>
+        <v>92124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,21 +1983,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2027,24 +2007,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mjöberget, Hls</t>
+          <t>Mjöberget norrsluttning, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542338</v>
+        <v>542450</v>
       </c>
       <c r="R13" t="n">
-        <v>6839706</v>
+        <v>6839795</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2086,45 +2066,30 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665683</t>
+          <t>https://artportalen.se/Sighting/136637408</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136694561</v>
+        <v>136637533</v>
       </c>
       <c r="B14" t="n">
-        <v>80485</v>
+        <v>96568</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,40 +2097,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mjöberget, Hls</t>
+          <t>Mjöberget norrsluttning, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542327</v>
+        <v>542476</v>
       </c>
       <c r="R14" t="n">
-        <v>6839655</v>
+        <v>6839720</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2195,11 +2161,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ymnigt på asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2215,81 +2176,77 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136694561</t>
+          <t>https://artportalen.se/Sighting/136637533</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136637626</v>
+        <v>136662522</v>
       </c>
       <c r="B15" t="n">
-        <v>99353</v>
+        <v>96568</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mjöberget norrsluttning, Hls</t>
+          <t>Mjöberget, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542512</v>
+        <v>542444</v>
       </c>
       <c r="R15" t="n">
-        <v>6839760</v>
+        <v>6839767</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2319,11 +2276,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sex överblommade stjälkar. En knärotskoloni som tydligt tagit skada av uttorkning och exponering efter att en väg byggts bara ca 30 m från den.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2339,27 +2291,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637626</t>
+          <t>https://artportalen.se/Sighting/136662522</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136694832</v>
+        <v>136665695</v>
       </c>
       <c r="B16" t="n">
-        <v>80541</v>
+        <v>96568</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,34 +2319,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2402,10 +2347,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542394</v>
+        <v>542338</v>
       </c>
       <c r="R16" t="n">
-        <v>6839595</v>
+        <v>6839706</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2440,11 +2385,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Grov asp</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2463,22 +2403,22 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136694832</t>
+          <t>https://artportalen.se/Sighting/136665695</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136694923</v>
+        <v>136921332</v>
       </c>
       <c r="B17" t="n">
-        <v>80541</v>
+        <v>96568</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2486,34 +2426,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2521,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542509</v>
+        <v>542517</v>
       </c>
       <c r="R17" t="n">
-        <v>6839587</v>
+        <v>6839739</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2559,11 +2492,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Grov asp</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2587,6 +2515,1751 @@
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921332</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136921363</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96568</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>542587</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6839433</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921363</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136921226</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>542419</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6839643</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>grov brannstubbe</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921226</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136921262</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>542405</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6839648</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hög brannstubbe med yxhugg</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921262</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136927764</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mjöberget norrsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>542418</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6839725</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer på kolade ytor på mycket grov och hög bränd tallstubbe.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136927764</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136662397</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>542452</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6839779</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136662397</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136665455</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>542418</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6839748</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136665455</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136665683</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>542338</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6839706</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136665683</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136694561</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>542327</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6839655</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ymnigt på asp</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136694561</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136921120</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>542588</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6839473</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ymnigt</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921120</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136921130</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99388</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>542481</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6839605</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921130</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136637626</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mjöberget norrsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>542512</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6839760</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Sex överblommade stjälkar. En knärotskoloni som tydligt tagit skada av uttorkning och exponering efter att en väg byggts bara ca 30 m från den.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Carina Frost, Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136637626</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136921330</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>542517</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6839739</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>8 blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921330</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136921359</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110098</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>542587</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6839433</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921359</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136694832</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80541</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>542394</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6839595</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Grov asp</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136694832</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136694923</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80541</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>542509</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6839587</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Grov asp</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136694923</t>
         </is>
@@ -2610,6 +4283,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662367</v>
       </c>
       <c r="B2" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -812,7 +812,7 @@
         <v>136662434</v>
       </c>
       <c r="B3" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>136665586</v>
       </c>
       <c r="B4" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>136665690</v>
       </c>
       <c r="B5" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136694564</v>
       </c>
       <c r="B6" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>136920950</v>
       </c>
       <c r="B7" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136920976</v>
       </c>
       <c r="B8" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136921075</v>
       </c>
       <c r="B9" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>136921117</v>
       </c>
       <c r="B10" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136921309</v>
       </c>
       <c r="B11" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921370</v>
       </c>
       <c r="B12" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>136637408</v>
       </c>
       <c r="B13" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>136637533</v>
       </c>
       <c r="B14" t="n">
-        <v>96568</v>
+        <v>96574</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136662522</v>
       </c>
       <c r="B15" t="n">
-        <v>96568</v>
+        <v>96574</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136665695</v>
       </c>
       <c r="B16" t="n">
-        <v>96568</v>
+        <v>96574</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136921332</v>
       </c>
       <c r="B17" t="n">
-        <v>96568</v>
+        <v>96574</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136921363</v>
       </c>
       <c r="B18" t="n">
-        <v>96568</v>
+        <v>96574</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136921226</v>
       </c>
       <c r="B19" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136921262</v>
       </c>
       <c r="B20" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>136927764</v>
       </c>
       <c r="B21" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136662397</v>
       </c>
       <c r="B22" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>136665455</v>
       </c>
       <c r="B23" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136665683</v>
       </c>
       <c r="B24" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136694561</v>
       </c>
       <c r="B25" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>136921120</v>
       </c>
       <c r="B26" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>136921130</v>
       </c>
       <c r="B27" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>136637626</v>
       </c>
       <c r="B28" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136921330</v>
       </c>
       <c r="B29" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>136921359</v>
       </c>
       <c r="B30" t="n">
-        <v>110098</v>
+        <v>110104</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>136694832</v>
       </c>
       <c r="B31" t="n">
-        <v>80541</v>
+        <v>80545</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136694923</v>
       </c>
       <c r="B32" t="n">
-        <v>80541</v>
+        <v>80545</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662367</v>
       </c>
       <c r="B2" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -812,7 +812,7 @@
         <v>136662434</v>
       </c>
       <c r="B3" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>136665586</v>
       </c>
       <c r="B4" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>136665690</v>
       </c>
       <c r="B5" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136694564</v>
       </c>
       <c r="B6" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>136920950</v>
       </c>
       <c r="B7" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136920976</v>
       </c>
       <c r="B8" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136921075</v>
       </c>
       <c r="B9" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>136921117</v>
       </c>
       <c r="B10" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136921309</v>
       </c>
       <c r="B11" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921370</v>
       </c>
       <c r="B12" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>136637408</v>
       </c>
       <c r="B13" t="n">
-        <v>92126</v>
+        <v>92128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>136637533</v>
       </c>
       <c r="B14" t="n">
-        <v>96574</v>
+        <v>96576</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136662522</v>
       </c>
       <c r="B15" t="n">
-        <v>96574</v>
+        <v>96576</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136665695</v>
       </c>
       <c r="B16" t="n">
-        <v>96574</v>
+        <v>96576</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136921332</v>
       </c>
       <c r="B17" t="n">
-        <v>96574</v>
+        <v>96576</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136921363</v>
       </c>
       <c r="B18" t="n">
-        <v>96574</v>
+        <v>96576</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136921226</v>
       </c>
       <c r="B19" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136921262</v>
       </c>
       <c r="B20" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>136927764</v>
       </c>
       <c r="B21" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136662397</v>
       </c>
       <c r="B22" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>136665455</v>
       </c>
       <c r="B23" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136665683</v>
       </c>
       <c r="B24" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136694561</v>
       </c>
       <c r="B25" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>136921120</v>
       </c>
       <c r="B26" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>136921130</v>
       </c>
       <c r="B27" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>136637626</v>
       </c>
       <c r="B28" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136921330</v>
       </c>
       <c r="B29" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>136921359</v>
       </c>
       <c r="B30" t="n">
-        <v>110104</v>
+        <v>110106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>136694832</v>
       </c>
       <c r="B31" t="n">
-        <v>80545</v>
+        <v>80547</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136694923</v>
       </c>
       <c r="B32" t="n">
-        <v>80545</v>
+        <v>80547</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662367</v>
       </c>
       <c r="B2" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>136662434</v>
       </c>
       <c r="B3" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>136665586</v>
       </c>
       <c r="B4" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>136665690</v>
       </c>
       <c r="B5" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136694564</v>
       </c>
       <c r="B6" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>136920950</v>
       </c>
       <c r="B7" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136920976</v>
       </c>
       <c r="B8" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136921075</v>
       </c>
       <c r="B9" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>136921117</v>
       </c>
       <c r="B10" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136921309</v>
       </c>
       <c r="B11" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921370</v>
       </c>
       <c r="B12" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>136637408</v>
       </c>
       <c r="B13" t="n">
-        <v>92128</v>
+        <v>92129</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>136637533</v>
       </c>
       <c r="B14" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136662522</v>
       </c>
       <c r="B15" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136665695</v>
       </c>
       <c r="B16" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136921332</v>
       </c>
       <c r="B17" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136921363</v>
       </c>
       <c r="B18" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136921226</v>
       </c>
       <c r="B19" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136921262</v>
       </c>
       <c r="B20" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>136927764</v>
       </c>
       <c r="B21" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136662397</v>
       </c>
       <c r="B22" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>136665455</v>
       </c>
       <c r="B23" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136665683</v>
       </c>
       <c r="B24" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136694561</v>
       </c>
       <c r="B25" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>136921120</v>
       </c>
       <c r="B26" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>136921130</v>
       </c>
       <c r="B27" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>136637626</v>
       </c>
       <c r="B28" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136921330</v>
       </c>
       <c r="B29" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>136921359</v>
       </c>
       <c r="B30" t="n">
-        <v>110106</v>
+        <v>110107</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>136694832</v>
       </c>
       <c r="B31" t="n">
-        <v>80547</v>
+        <v>80548</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136694923</v>
       </c>
       <c r="B32" t="n">
-        <v>80547</v>
+        <v>80548</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -1975,7 +1975,7 @@
         <v>136637408</v>
       </c>
       <c r="B13" t="n">
-        <v>92129</v>
+        <v>92135</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>136637533</v>
       </c>
       <c r="B14" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136662522</v>
       </c>
       <c r="B15" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136665695</v>
       </c>
       <c r="B16" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136921332</v>
       </c>
       <c r="B17" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136921363</v>
       </c>
       <c r="B18" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>136921130</v>
       </c>
       <c r="B27" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>136637626</v>
       </c>
       <c r="B28" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136921330</v>
       </c>
       <c r="B29" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>136921359</v>
       </c>
       <c r="B30" t="n">
-        <v>110107</v>
+        <v>110113</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662367</v>
       </c>
       <c r="B2" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>136662434</v>
       </c>
       <c r="B3" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>136665586</v>
       </c>
       <c r="B4" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>136665690</v>
       </c>
       <c r="B5" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>136694564</v>
       </c>
       <c r="B6" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>136920950</v>
       </c>
       <c r="B7" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136920976</v>
       </c>
       <c r="B8" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136921075</v>
       </c>
       <c r="B9" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>136921117</v>
       </c>
       <c r="B10" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136921309</v>
       </c>
       <c r="B11" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921370</v>
       </c>
       <c r="B12" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>136637408</v>
       </c>
       <c r="B13" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>136637533</v>
       </c>
       <c r="B14" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136662522</v>
       </c>
       <c r="B15" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136665695</v>
       </c>
       <c r="B16" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136921332</v>
       </c>
       <c r="B17" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>136921363</v>
       </c>
       <c r="B18" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136921226</v>
       </c>
       <c r="B19" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136921262</v>
       </c>
       <c r="B20" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>136927764</v>
       </c>
       <c r="B21" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136662397</v>
       </c>
       <c r="B22" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>136665455</v>
       </c>
       <c r="B23" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136665683</v>
       </c>
       <c r="B24" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136694561</v>
       </c>
       <c r="B25" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>136921120</v>
       </c>
       <c r="B26" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>136921130</v>
       </c>
       <c r="B27" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>136637626</v>
       </c>
       <c r="B28" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>136921330</v>
       </c>
       <c r="B29" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>136921359</v>
       </c>
       <c r="B30" t="n">
-        <v>110113</v>
+        <v>110117</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>136694832</v>
       </c>
       <c r="B31" t="n">
-        <v>80548</v>
+        <v>80550</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136694923</v>
       </c>
       <c r="B32" t="n">
-        <v>80548</v>
+        <v>80550</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,44 +680,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136662367</v>
+        <v>137184946</v>
       </c>
       <c r="B2" t="n">
-        <v>80463</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>392</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Degel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542452</v>
+        <v>542367</v>
       </c>
       <c r="R2" t="n">
-        <v>6839801</v>
+        <v>6839609</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,21 +766,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -797,19 +774,19 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136662367</t>
+          <t>https://artportalen.se/Sighting/137184946</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136662434</v>
+        <v>136662367</v>
       </c>
       <c r="B3" t="n">
         <v>80463</v>
@@ -855,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542443</v>
+        <v>542452</v>
       </c>
       <c r="R3" t="n">
-        <v>6839775</v>
+        <v>6839801</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -926,19 +903,19 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136662434</t>
+          <t>https://artportalen.se/Sighting/136662367</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136665586</v>
+        <v>136662434</v>
       </c>
       <c r="B4" t="n">
         <v>80463</v>
@@ -968,7 +945,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542404</v>
+        <v>542443</v>
       </c>
       <c r="R4" t="n">
-        <v>6839722</v>
+        <v>6839775</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1061,13 +1038,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665586</t>
+          <t>https://artportalen.se/Sighting/136662434</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136665690</v>
+        <v>136665586</v>
       </c>
       <c r="B5" t="n">
         <v>80463</v>
@@ -1095,8 +1072,16 @@
           <t>Degel.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1105,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542338</v>
+        <v>542404</v>
       </c>
       <c r="R5" t="n">
-        <v>6839706</v>
+        <v>6839722</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1182,13 +1167,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665690</t>
+          <t>https://artportalen.se/Sighting/136665586</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136694564</v>
+        <v>136665690</v>
       </c>
       <c r="B6" t="n">
         <v>80463</v>
@@ -1226,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542327</v>
+        <v>542338</v>
       </c>
       <c r="R6" t="n">
-        <v>6839655</v>
+        <v>6839706</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1264,11 +1249,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ymnigt på asp</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1279,6 +1259,21 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1293,13 +1288,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136694564</t>
+          <t>https://artportalen.se/Sighting/136665690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136920950</v>
+        <v>136694564</v>
       </c>
       <c r="B7" t="n">
         <v>80463</v>
@@ -1327,16 +1322,8 @@
           <t>Degel.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1345,10 +1332,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542474</v>
+        <v>542327</v>
       </c>
       <c r="R7" t="n">
-        <v>6839441</v>
+        <v>6839655</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1383,6 +1370,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ymnigt på asp</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1407,13 +1399,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136920950</t>
+          <t>https://artportalen.se/Sighting/136694564</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136920976</v>
+        <v>136920950</v>
       </c>
       <c r="B8" t="n">
         <v>80463</v>
@@ -1443,7 +1435,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1459,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542517</v>
+        <v>542474</v>
       </c>
       <c r="R8" t="n">
-        <v>6839397</v>
+        <v>6839441</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1521,13 +1513,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136920976</t>
+          <t>https://artportalen.se/Sighting/136920950</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136921075</v>
+        <v>136920976</v>
       </c>
       <c r="B9" t="n">
         <v>80463</v>
@@ -1557,7 +1549,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1573,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542584</v>
+        <v>542517</v>
       </c>
       <c r="R9" t="n">
-        <v>6839474</v>
+        <v>6839397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1635,13 +1627,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921075</t>
+          <t>https://artportalen.se/Sighting/136920976</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136921117</v>
+        <v>136921075</v>
       </c>
       <c r="B10" t="n">
         <v>80463</v>
@@ -1669,8 +1661,16 @@
           <t>Degel.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542588</v>
+        <v>542584</v>
       </c>
       <c r="R10" t="n">
-        <v>6839473</v>
+        <v>6839474</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1717,11 +1717,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ymnigt</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1746,13 +1741,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921117</t>
+          <t>https://artportalen.se/Sighting/136921075</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136921309</v>
+        <v>136921117</v>
       </c>
       <c r="B11" t="n">
         <v>80463</v>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542484</v>
+        <v>542588</v>
       </c>
       <c r="R11" t="n">
-        <v>6839710</v>
+        <v>6839473</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,6 +1823,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ymnigt</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1852,13 +1852,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921309</t>
+          <t>https://artportalen.se/Sighting/136921117</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136921370</v>
+        <v>136921309</v>
       </c>
       <c r="B12" t="n">
         <v>80463</v>
@@ -1886,16 +1886,8 @@
           <t>Degel.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1904,10 +1896,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542587</v>
+        <v>542484</v>
       </c>
       <c r="R12" t="n">
-        <v>6839433</v>
+        <v>6839710</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1960,71 +1952,71 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921370</t>
+          <t>https://artportalen.se/Sighting/136921309</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136637408</v>
+        <v>136921370</v>
       </c>
       <c r="B13" t="n">
-        <v>92139</v>
+        <v>80463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>392</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mjöberget norrsluttning, Hls</t>
+          <t>Mjöberget, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542450</v>
+        <v>542587</v>
       </c>
       <c r="R13" t="n">
-        <v>6839795</v>
+        <v>6839433</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2069,27 +2061,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637408</t>
+          <t>https://artportalen.se/Sighting/136921370</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136637533</v>
+        <v>136637408</v>
       </c>
       <c r="B14" t="n">
-        <v>96587</v>
+        <v>92139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,27 +2089,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2125,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542476</v>
+        <v>542450</v>
       </c>
       <c r="R14" t="n">
-        <v>6839720</v>
+        <v>6839795</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2181,22 +2180,22 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637533</t>
+          <t>https://artportalen.se/Sighting/136637408</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136662522</v>
+        <v>136637533</v>
       </c>
       <c r="B15" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,32 +2220,24 @@
           <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mjöberget, Hls</t>
+          <t>Mjöberget norrsluttning, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542444</v>
+        <v>542476</v>
       </c>
       <c r="R15" t="n">
-        <v>6839767</v>
+        <v>6839720</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2291,27 +2282,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136662522</t>
+          <t>https://artportalen.se/Sighting/136637533</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136665695</v>
+        <v>136662522</v>
       </c>
       <c r="B16" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,8 +2327,16 @@
           <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2347,10 +2346,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542338</v>
+        <v>542444</v>
       </c>
       <c r="R16" t="n">
-        <v>6839706</v>
+        <v>6839767</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2409,16 +2408,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665695</t>
+          <t>https://artportalen.se/Sighting/136662522</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136921332</v>
+        <v>136665695</v>
       </c>
       <c r="B17" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,10 +2453,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542517</v>
+        <v>542338</v>
       </c>
       <c r="R17" t="n">
-        <v>6839739</v>
+        <v>6839706</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2510,22 +2509,22 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921332</t>
+          <t>https://artportalen.se/Sighting/136665695</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136921363</v>
+        <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542587</v>
+        <v>542517</v>
       </c>
       <c r="R18" t="n">
-        <v>6839433</v>
+        <v>6839739</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2623,43 +2622,44 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921363</t>
+          <t>https://artportalen.se/Sighting/136921332</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136921226</v>
+        <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>79242</v>
+        <v>96589</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542419</v>
+        <v>542587</v>
       </c>
       <c r="R19" t="n">
-        <v>6839643</v>
+        <v>6839433</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2705,11 +2705,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>grov brannstubbe</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2728,19 +2723,19 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921226</t>
+          <t>https://artportalen.se/Sighting/136921363</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136921262</v>
+        <v>136921226</v>
       </c>
       <c r="B20" t="n">
         <v>79242</v>
@@ -2778,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542405</v>
+        <v>542419</v>
       </c>
       <c r="R20" t="n">
-        <v>6839648</v>
+        <v>6839643</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2818,7 +2813,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>hög brannstubbe med yxhugg</t>
+          <t>grov brannstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,13 +2840,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921262</t>
+          <t>https://artportalen.se/Sighting/136921226</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136927764</v>
+        <v>136921262</v>
       </c>
       <c r="B21" t="n">
         <v>79242</v>
@@ -2885,17 +2880,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mjöberget norrsluttning, Hls</t>
+          <t>Mjöberget, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542418</v>
+        <v>542405</v>
       </c>
       <c r="R21" t="n">
-        <v>6839725</v>
+        <v>6839648</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2929,7 +2924,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Växer på kolade ytor på mycket grov och hög bränd tallstubbe.</t>
+          <t>hög brannstubbe med yxhugg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,49 +2940,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136927764</t>
+          <t>https://artportalen.se/Sighting/136921262</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136662397</v>
+        <v>136927764</v>
       </c>
       <c r="B22" t="n">
-        <v>80494</v>
+        <v>79242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2996,17 +2991,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mjöberget, Hls</t>
+          <t>Mjöberget norrsluttning, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542452</v>
+        <v>542418</v>
       </c>
       <c r="R22" t="n">
-        <v>6839779</v>
+        <v>6839725</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3036,6 +3031,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer på kolade ytor på mycket grov och hög bränd tallstubbe.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,42 +3048,27 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136662397</t>
+          <t>https://artportalen.se/Sighting/136927764</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136665455</v>
+        <v>136662397</v>
       </c>
       <c r="B23" t="n">
         <v>80494</v>
@@ -3111,16 +3096,8 @@
           <t>(Dicks.) Nyl.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3129,10 +3106,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542418</v>
+        <v>542452</v>
       </c>
       <c r="R23" t="n">
-        <v>6839748</v>
+        <v>6839779</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3206,13 +3183,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665455</t>
+          <t>https://artportalen.se/Sighting/136662397</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136665683</v>
+        <v>136665455</v>
       </c>
       <c r="B24" t="n">
         <v>80494</v>
@@ -3242,7 +3219,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3258,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542338</v>
+        <v>542418</v>
       </c>
       <c r="R24" t="n">
-        <v>6839706</v>
+        <v>6839748</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3335,13 +3312,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665683</t>
+          <t>https://artportalen.se/Sighting/136665455</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136694561</v>
+        <v>136665683</v>
       </c>
       <c r="B25" t="n">
         <v>80494</v>
@@ -3369,8 +3346,16 @@
           <t>(Dicks.) Nyl.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3379,10 +3364,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542327</v>
+        <v>542338</v>
       </c>
       <c r="R25" t="n">
-        <v>6839655</v>
+        <v>6839706</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3417,11 +3402,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ymnigt på asp</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3432,6 +3412,21 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3446,13 +3441,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136694561</t>
+          <t>https://artportalen.se/Sighting/136665683</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136921120</v>
+        <v>136694561</v>
       </c>
       <c r="B26" t="n">
         <v>80494</v>
@@ -3490,10 +3485,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542588</v>
+        <v>542327</v>
       </c>
       <c r="R26" t="n">
-        <v>6839473</v>
+        <v>6839655</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3530,7 +3525,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ymnigt</t>
+          <t>Ymnigt på asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3557,16 +3552,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921120</t>
+          <t>https://artportalen.se/Sighting/136694561</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136921130</v>
+        <v>136921120</v>
       </c>
       <c r="B27" t="n">
-        <v>99407</v>
+        <v>80494</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3574,35 +3569,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219874</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3610,10 +3596,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542481</v>
+        <v>542588</v>
       </c>
       <c r="R27" t="n">
-        <v>6839605</v>
+        <v>6839473</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3648,6 +3634,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ymnigt</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3666,49 +3657,49 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921130</t>
+          <t>https://artportalen.se/Sighting/136921120</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136637626</v>
+        <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99372</v>
+        <v>99409</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3716,26 +3707,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mjöberget norrsluttning, Hls</t>
+          <t>Mjöberget, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542512</v>
+        <v>542481</v>
       </c>
       <c r="R28" t="n">
-        <v>6839760</v>
+        <v>6839605</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3765,11 +3752,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Sex överblommade stjälkar. En knärotskoloni som tydligt tagit skada av uttorkning och exponering efter att en väg byggts bara ca 30 m från den.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,27 +3767,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136637626</t>
+          <t>https://artportalen.se/Sighting/136921130</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136921330</v>
+        <v>136637626</v>
       </c>
       <c r="B29" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,30 +3814,34 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mjöberget, Hls</t>
+          <t>Mjöberget norrsluttning, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542517</v>
+        <v>542512</v>
       </c>
       <c r="R29" t="n">
-        <v>6839739</v>
+        <v>6839760</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3889,7 +3875,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>8 blomstjälkar</t>
+          <t>Sex överblommade stjälkar. En knärotskoloni som tydligt tagit skada av uttorkning och exponering efter att en väg byggts bara ca 30 m från den.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3905,53 +3891,61 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921330</t>
+          <t>https://artportalen.se/Sighting/136637626</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136921359</v>
+        <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>110117</v>
+        <v>99374</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221184</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3961,10 +3955,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542587</v>
+        <v>542517</v>
       </c>
       <c r="R30" t="n">
-        <v>6839433</v>
+        <v>6839739</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3999,6 +3993,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>8 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4023,16 +4022,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921359</t>
+          <t>https://artportalen.se/Sighting/136921330</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136694832</v>
+        <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>80550</v>
+        <v>110119</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4040,34 +4039,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>221184</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4075,10 +4067,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542394</v>
+        <v>542587</v>
       </c>
       <c r="R31" t="n">
-        <v>6839595</v>
+        <v>6839433</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4113,11 +4105,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Grov asp</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4142,13 +4129,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136694832</t>
+          <t>https://artportalen.se/Sighting/136921359</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136694923</v>
+        <v>136694832</v>
       </c>
       <c r="B32" t="n">
         <v>80550</v>
@@ -4178,12 +4165,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -4194,10 +4181,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542509</v>
+        <v>542394</v>
       </c>
       <c r="R32" t="n">
-        <v>6839587</v>
+        <v>6839595</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4260,6 +4247,125 @@
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136694832</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136694923</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80550</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mjöberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>542509</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6839587</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Grov asp</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136694923</t>
         </is>
@@ -4298,6 +4404,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184946</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136662367</v>
       </c>
       <c r="B3" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -918,7 +918,7 @@
         <v>136662434</v>
       </c>
       <c r="B4" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136665586</v>
       </c>
       <c r="B5" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>136665690</v>
       </c>
       <c r="B6" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136694564</v>
       </c>
       <c r="B7" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136920950</v>
       </c>
       <c r="B8" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136920976</v>
       </c>
       <c r="B9" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>136921075</v>
       </c>
       <c r="B10" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136921117</v>
       </c>
       <c r="B11" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921309</v>
       </c>
       <c r="B12" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136921370</v>
       </c>
       <c r="B13" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136637408</v>
       </c>
       <c r="B14" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136637533</v>
       </c>
       <c r="B15" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>136662522</v>
       </c>
       <c r="B16" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136665695</v>
       </c>
       <c r="B17" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136921226</v>
       </c>
       <c r="B20" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136921262</v>
       </c>
       <c r="B21" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136927764</v>
       </c>
       <c r="B22" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>136662397</v>
       </c>
       <c r="B23" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>136665455</v>
       </c>
       <c r="B24" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>136665683</v>
       </c>
       <c r="B25" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136694561</v>
       </c>
       <c r="B26" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136921120</v>
       </c>
       <c r="B27" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>136637626</v>
       </c>
       <c r="B29" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110119</v>
+        <v>110121</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>136694832</v>
       </c>
       <c r="B32" t="n">
-        <v>80550</v>
+        <v>80553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>136694923</v>
       </c>
       <c r="B33" t="n">
-        <v>80550</v>
+        <v>80553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184946</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136662367</v>
       </c>
       <c r="B3" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -918,7 +918,7 @@
         <v>136662434</v>
       </c>
       <c r="B4" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136665586</v>
       </c>
       <c r="B5" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>136665690</v>
       </c>
       <c r="B6" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136694564</v>
       </c>
       <c r="B7" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136920950</v>
       </c>
       <c r="B8" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136920976</v>
       </c>
       <c r="B9" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>136921075</v>
       </c>
       <c r="B10" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136921117</v>
       </c>
       <c r="B11" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921309</v>
       </c>
       <c r="B12" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136921370</v>
       </c>
       <c r="B13" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136637408</v>
       </c>
       <c r="B14" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136637533</v>
       </c>
       <c r="B15" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>136662522</v>
       </c>
       <c r="B16" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136665695</v>
       </c>
       <c r="B17" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136921226</v>
       </c>
       <c r="B20" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136921262</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136927764</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>136662397</v>
       </c>
       <c r="B23" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>136665455</v>
       </c>
       <c r="B24" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>136665683</v>
       </c>
       <c r="B25" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136694561</v>
       </c>
       <c r="B26" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136921120</v>
       </c>
       <c r="B27" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>136637626</v>
       </c>
       <c r="B29" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110121</v>
+        <v>110134</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>136694832</v>
       </c>
       <c r="B32" t="n">
-        <v>80553</v>
+        <v>80566</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>136694923</v>
       </c>
       <c r="B33" t="n">
-        <v>80553</v>
+        <v>80566</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184946</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136662367</v>
       </c>
       <c r="B3" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136662434</v>
       </c>
       <c r="B4" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136665586</v>
       </c>
       <c r="B5" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>136665690</v>
       </c>
       <c r="B6" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>136694564</v>
       </c>
       <c r="B7" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136920950</v>
       </c>
       <c r="B8" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136920976</v>
       </c>
       <c r="B9" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>136921075</v>
       </c>
       <c r="B10" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136921117</v>
       </c>
       <c r="B11" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921309</v>
       </c>
       <c r="B12" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136921370</v>
       </c>
       <c r="B13" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136637408</v>
       </c>
       <c r="B14" t="n">
-        <v>92154</v>
+        <v>92156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136637533</v>
       </c>
       <c r="B15" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>136662522</v>
       </c>
       <c r="B16" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136665695</v>
       </c>
       <c r="B17" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136921226</v>
       </c>
       <c r="B20" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136921262</v>
       </c>
       <c r="B21" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136927764</v>
       </c>
       <c r="B22" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>136662397</v>
       </c>
       <c r="B23" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>136665455</v>
       </c>
       <c r="B24" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>136665683</v>
       </c>
       <c r="B25" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136694561</v>
       </c>
       <c r="B26" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136921120</v>
       </c>
       <c r="B27" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>136637626</v>
       </c>
       <c r="B29" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110134</v>
+        <v>110136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>136694832</v>
       </c>
       <c r="B32" t="n">
-        <v>80566</v>
+        <v>80568</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>136694923</v>
       </c>
       <c r="B33" t="n">
-        <v>80566</v>
+        <v>80568</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -2302,7 +2302,7 @@
         <v>136662522</v>
       </c>
       <c r="B16" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136665695</v>
       </c>
       <c r="B17" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110136</v>
+        <v>110141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184946</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136662367</v>
       </c>
       <c r="B3" t="n">
-        <v>80481</v>
+        <v>80491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136920950</v>
       </c>
       <c r="B8" t="n">
-        <v>80481</v>
+        <v>80491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136920976</v>
       </c>
       <c r="B9" t="n">
-        <v>80481</v>
+        <v>80491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>136921075</v>
       </c>
       <c r="B10" t="n">
-        <v>80481</v>
+        <v>80491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136921117</v>
       </c>
       <c r="B11" t="n">
-        <v>80481</v>
+        <v>80491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921309</v>
       </c>
       <c r="B12" t="n">
-        <v>80481</v>
+        <v>80491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136921370</v>
       </c>
       <c r="B13" t="n">
-        <v>80481</v>
+        <v>80491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136921226</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136921262</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136927764</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136921120</v>
       </c>
       <c r="B27" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110141</v>
+        <v>110162</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184946</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136662367</v>
       </c>
       <c r="B3" t="n">
-        <v>80491</v>
+        <v>80494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136920950</v>
       </c>
       <c r="B8" t="n">
-        <v>80491</v>
+        <v>80494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136920976</v>
       </c>
       <c r="B9" t="n">
-        <v>80491</v>
+        <v>80494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>136921075</v>
       </c>
       <c r="B10" t="n">
-        <v>80491</v>
+        <v>80494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136921117</v>
       </c>
       <c r="B11" t="n">
-        <v>80491</v>
+        <v>80494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921309</v>
       </c>
       <c r="B12" t="n">
-        <v>80491</v>
+        <v>80494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136921370</v>
       </c>
       <c r="B13" t="n">
-        <v>80491</v>
+        <v>80494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136921226</v>
       </c>
       <c r="B20" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136921262</v>
       </c>
       <c r="B21" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136927764</v>
       </c>
       <c r="B22" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136921120</v>
       </c>
       <c r="B27" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110163</v>
+        <v>110168</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110168</v>
+        <v>110171</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184946</v>
       </c>
       <c r="B2" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136662367</v>
       </c>
       <c r="B3" t="n">
-        <v>80494</v>
+        <v>80499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136920950</v>
       </c>
       <c r="B8" t="n">
-        <v>80494</v>
+        <v>80499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136920976</v>
       </c>
       <c r="B9" t="n">
-        <v>80494</v>
+        <v>80499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>136921075</v>
       </c>
       <c r="B10" t="n">
-        <v>80494</v>
+        <v>80499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136921117</v>
       </c>
       <c r="B11" t="n">
-        <v>80494</v>
+        <v>80499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921309</v>
       </c>
       <c r="B12" t="n">
-        <v>80494</v>
+        <v>80499</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136921370</v>
       </c>
       <c r="B13" t="n">
-        <v>80494</v>
+        <v>80499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136921226</v>
       </c>
       <c r="B20" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136921262</v>
       </c>
       <c r="B21" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136927764</v>
       </c>
       <c r="B22" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136921120</v>
       </c>
       <c r="B27" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110171</v>
+        <v>110177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110177</v>
+        <v>110178</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184946</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136662367</v>
       </c>
       <c r="B3" t="n">
-        <v>80499</v>
+        <v>80510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136920950</v>
       </c>
       <c r="B8" t="n">
-        <v>80499</v>
+        <v>80510</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136920976</v>
       </c>
       <c r="B9" t="n">
-        <v>80499</v>
+        <v>80510</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>136921075</v>
       </c>
       <c r="B10" t="n">
-        <v>80499</v>
+        <v>80510</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136921117</v>
       </c>
       <c r="B11" t="n">
-        <v>80499</v>
+        <v>80510</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921309</v>
       </c>
       <c r="B12" t="n">
-        <v>80499</v>
+        <v>80510</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136921370</v>
       </c>
       <c r="B13" t="n">
-        <v>80499</v>
+        <v>80510</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136921226</v>
       </c>
       <c r="B20" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136921262</v>
       </c>
       <c r="B21" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136927764</v>
       </c>
       <c r="B22" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136921120</v>
       </c>
       <c r="B27" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110178</v>
+        <v>110190</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184946</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136662367</v>
       </c>
       <c r="B3" t="n">
-        <v>80510</v>
+        <v>80511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136920950</v>
       </c>
       <c r="B8" t="n">
-        <v>80510</v>
+        <v>80511</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136920976</v>
       </c>
       <c r="B9" t="n">
-        <v>80510</v>
+        <v>80511</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>136921075</v>
       </c>
       <c r="B10" t="n">
-        <v>80510</v>
+        <v>80511</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136921117</v>
       </c>
       <c r="B11" t="n">
-        <v>80510</v>
+        <v>80511</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921309</v>
       </c>
       <c r="B12" t="n">
-        <v>80510</v>
+        <v>80511</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136921370</v>
       </c>
       <c r="B13" t="n">
-        <v>80510</v>
+        <v>80511</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136921226</v>
       </c>
       <c r="B20" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136921262</v>
       </c>
       <c r="B21" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136927764</v>
       </c>
       <c r="B22" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136921120</v>
       </c>
       <c r="B27" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110190</v>
+        <v>110191</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184946</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136662367</v>
       </c>
       <c r="B3" t="n">
-        <v>80511</v>
+        <v>80513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136920950</v>
       </c>
       <c r="B8" t="n">
-        <v>80511</v>
+        <v>80513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136920976</v>
       </c>
       <c r="B9" t="n">
-        <v>80511</v>
+        <v>80513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>136921075</v>
       </c>
       <c r="B10" t="n">
-        <v>80511</v>
+        <v>80513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136921117</v>
       </c>
       <c r="B11" t="n">
-        <v>80511</v>
+        <v>80513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136921309</v>
       </c>
       <c r="B12" t="n">
-        <v>80511</v>
+        <v>80513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136921370</v>
       </c>
       <c r="B13" t="n">
-        <v>80511</v>
+        <v>80513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>136921332</v>
       </c>
       <c r="B18" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136921363</v>
       </c>
       <c r="B19" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136921226</v>
       </c>
       <c r="B20" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136921262</v>
       </c>
       <c r="B21" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136927764</v>
       </c>
       <c r="B22" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136921120</v>
       </c>
       <c r="B27" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136921130</v>
       </c>
       <c r="B28" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136921330</v>
       </c>
       <c r="B30" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>136921359</v>
       </c>
       <c r="B31" t="n">
-        <v>110191</v>
+        <v>110194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 35543-2026 artfynd.xlsx
+++ b/artfynd/A 35543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184946</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
